--- a/data/processed/terremotos_procesados_reshape_test.xlsx
+++ b/data/processed/terremotos_procesados_reshape_test.xlsx
@@ -502,7 +502,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B2">
         <v>34</v>
@@ -514,40 +514,40 @@
         <v>2026</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2">
+        <v>33</v>
+      </c>
+      <c r="G2">
         <v>43</v>
       </c>
-      <c r="G2">
-        <v>34</v>
-      </c>
       <c r="H2">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J2">
         <v>34</v>
       </c>
       <c r="K2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L2">
+        <v>29</v>
+      </c>
+      <c r="M2">
         <v>48</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>40</v>
       </c>
-      <c r="N2">
-        <v>46</v>
-      </c>
       <c r="O2">
+        <v>46</v>
+      </c>
+      <c r="P2">
         <v>41</v>
-      </c>
-      <c r="P2">
-        <v>49</v>
       </c>
       <c r="Q2">
         <v>36.66666666666666</v>
@@ -556,18 +556,18 @@
         <v>38</v>
       </c>
       <c r="S2">
-        <v>36.55554040022041</v>
+        <v>35.2777702001102</v>
       </c>
       <c r="T2">
-        <v>37.5025287839951</v>
+        <v>36.33501918933007</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C3">
         <v>9</v>
@@ -579,57 +579,57 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3">
+        <v>33</v>
+      </c>
+      <c r="H3">
         <v>43</v>
       </c>
-      <c r="H3">
-        <v>34</v>
-      </c>
       <c r="I3">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="J3">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K3">
         <v>34</v>
       </c>
       <c r="L3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M3">
+        <v>29</v>
+      </c>
+      <c r="N3">
         <v>48</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>40</v>
       </c>
-      <c r="O3">
-        <v>46</v>
-      </c>
       <c r="P3">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q3">
-        <v>36.66666666666666</v>
+        <v>33.66666666666666</v>
       </c>
       <c r="R3">
-        <v>38</v>
+        <v>35.6</v>
       </c>
       <c r="S3">
-        <v>35.2777702001102</v>
+        <v>34.63888510005511</v>
       </c>
       <c r="T3">
-        <v>36.33501918933007</v>
+        <v>35.55667945955338</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B4">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -638,60 +638,60 @@
         <v>2026</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F4">
         <v>34</v>
       </c>
       <c r="G4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4">
+        <v>33</v>
+      </c>
+      <c r="I4">
         <v>43</v>
       </c>
-      <c r="I4">
-        <v>34</v>
-      </c>
       <c r="J4">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="K4">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="L4">
         <v>34</v>
       </c>
       <c r="M4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="N4">
+        <v>29</v>
+      </c>
+      <c r="O4">
         <v>48</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>40</v>
       </c>
-      <c r="P4">
-        <v>46</v>
-      </c>
       <c r="Q4">
-        <v>33.66666666666666</v>
+        <v>38</v>
       </c>
       <c r="R4">
-        <v>35.6</v>
+        <v>38</v>
       </c>
       <c r="S4">
-        <v>34.63888510005511</v>
+        <v>40.31944255002755</v>
       </c>
       <c r="T4">
-        <v>35.55667945955338</v>
+        <v>39.03778630636892</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="2">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B5">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -700,60 +700,60 @@
         <v>2026</v>
       </c>
       <c r="E5">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G5">
         <v>34</v>
       </c>
       <c r="H5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I5">
+        <v>33</v>
+      </c>
+      <c r="J5">
         <v>43</v>
       </c>
-      <c r="J5">
-        <v>34</v>
-      </c>
       <c r="K5">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="L5">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="M5">
         <v>34</v>
       </c>
       <c r="N5">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="O5">
+        <v>29</v>
+      </c>
+      <c r="P5">
         <v>48</v>
       </c>
-      <c r="P5">
-        <v>40</v>
-      </c>
       <c r="Q5">
-        <v>38</v>
+        <v>36.33333333333334</v>
       </c>
       <c r="R5">
-        <v>38</v>
+        <v>35.2</v>
       </c>
       <c r="S5">
-        <v>40.31944255002755</v>
+        <v>34.65972127501378</v>
       </c>
       <c r="T5">
-        <v>39.03778630636892</v>
+        <v>35.69185753757928</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="2">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>9</v>
@@ -762,60 +762,60 @@
         <v>2026</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F6">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H6">
         <v>34</v>
       </c>
       <c r="I6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J6">
+        <v>33</v>
+      </c>
+      <c r="K6">
         <v>43</v>
       </c>
-      <c r="K6">
-        <v>34</v>
-      </c>
       <c r="L6">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="M6">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="N6">
         <v>34</v>
       </c>
       <c r="O6">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P6">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="Q6">
-        <v>36.33333333333334</v>
+        <v>37.66666666666666</v>
       </c>
       <c r="R6">
-        <v>35.2</v>
+        <v>36.2</v>
       </c>
       <c r="S6">
-        <v>34.65972127501378</v>
+        <v>36.32986063750689</v>
       </c>
       <c r="T6">
-        <v>35.69185753757928</v>
+        <v>36.46123835838619</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -824,60 +824,60 @@
         <v>2026</v>
       </c>
       <c r="E7">
+        <v>36</v>
+      </c>
+      <c r="F7">
         <v>38</v>
       </c>
-      <c r="F7">
-        <v>29</v>
-      </c>
       <c r="G7">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="H7">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="I7">
         <v>34</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K7">
+        <v>33</v>
+      </c>
+      <c r="L7">
         <v>43</v>
       </c>
-      <c r="L7">
-        <v>34</v>
-      </c>
       <c r="M7">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="N7">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="O7">
         <v>34</v>
       </c>
       <c r="P7">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q7">
-        <v>37.66666666666666</v>
+        <v>34.33333333333334</v>
       </c>
       <c r="R7">
-        <v>36.2</v>
+        <v>36.6</v>
       </c>
       <c r="S7">
-        <v>36.32986063750689</v>
+        <v>36.16493031875345</v>
       </c>
       <c r="T7">
-        <v>36.46123835838619</v>
+        <v>36.30749223892413</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>9</v>
@@ -886,57 +886,57 @@
         <v>2026</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F8">
+        <v>36</v>
+      </c>
+      <c r="G8">
         <v>38</v>
       </c>
-      <c r="G8">
-        <v>29</v>
-      </c>
       <c r="H8">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="I8">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J8">
         <v>34</v>
       </c>
       <c r="K8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L8">
+        <v>33</v>
+      </c>
+      <c r="M8">
         <v>43</v>
       </c>
-      <c r="M8">
-        <v>34</v>
-      </c>
       <c r="N8">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="O8">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="P8">
         <v>34</v>
       </c>
       <c r="Q8">
-        <v>34.33333333333334</v>
+        <v>35.66666666666666</v>
       </c>
       <c r="R8">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="S8">
-        <v>36.16493031875345</v>
+        <v>34.58246515937672</v>
       </c>
       <c r="T8">
-        <v>36.30749223892413</v>
+        <v>35.20499482594942</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B9">
         <v>32</v>
@@ -948,60 +948,60 @@
         <v>2026</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G9">
+        <v>36</v>
+      </c>
+      <c r="H9">
         <v>38</v>
       </c>
-      <c r="H9">
-        <v>29</v>
-      </c>
       <c r="I9">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="J9">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K9">
         <v>34</v>
       </c>
       <c r="L9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M9">
+        <v>33</v>
+      </c>
+      <c r="N9">
         <v>43</v>
       </c>
-      <c r="N9">
-        <v>34</v>
-      </c>
       <c r="O9">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="P9">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q9">
-        <v>35.66666666666666</v>
+        <v>33.66666666666666</v>
       </c>
       <c r="R9">
-        <v>36.4</v>
+        <v>33.6</v>
       </c>
       <c r="S9">
-        <v>34.58246515937672</v>
+        <v>33.29123257968836</v>
       </c>
       <c r="T9">
-        <v>35.20499482594942</v>
+        <v>34.13666321729961</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B10">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1013,57 +1013,57 @@
         <v>32</v>
       </c>
       <c r="F10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H10">
+        <v>36</v>
+      </c>
+      <c r="I10">
         <v>38</v>
       </c>
-      <c r="I10">
-        <v>29</v>
-      </c>
       <c r="J10">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="K10">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="L10">
         <v>34</v>
       </c>
       <c r="M10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N10">
+        <v>33</v>
+      </c>
+      <c r="O10">
         <v>43</v>
       </c>
-      <c r="O10">
-        <v>34</v>
-      </c>
       <c r="P10">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="Q10">
-        <v>33.66666666666666</v>
+        <v>32.33333333333334</v>
       </c>
       <c r="R10">
-        <v>33.6</v>
+        <v>34.2</v>
       </c>
       <c r="S10">
-        <v>33.29123257968836</v>
+        <v>32.64561628984418</v>
       </c>
       <c r="T10">
-        <v>34.13666321729961</v>
+        <v>33.42444214486641</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B11">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -1072,60 +1072,60 @@
         <v>2026</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F11">
         <v>32</v>
       </c>
       <c r="G11">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H11">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I11">
+        <v>36</v>
+      </c>
+      <c r="J11">
         <v>38</v>
       </c>
-      <c r="J11">
-        <v>29</v>
-      </c>
       <c r="K11">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="L11">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="M11">
         <v>34</v>
       </c>
       <c r="N11">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O11">
+        <v>33</v>
+      </c>
+      <c r="P11">
         <v>43</v>
       </c>
-      <c r="P11">
-        <v>34</v>
-      </c>
       <c r="Q11">
-        <v>32.33333333333334</v>
+        <v>33</v>
       </c>
       <c r="R11">
-        <v>34.2</v>
+        <v>33.6</v>
       </c>
       <c r="S11">
-        <v>32.64561628984418</v>
+        <v>33.82280814492209</v>
       </c>
       <c r="T11">
-        <v>33.42444214486641</v>
+        <v>33.94962809657761</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="2">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B12">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>9</v>
@@ -1134,60 +1134,60 @@
         <v>2026</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F12">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G12">
         <v>32</v>
       </c>
       <c r="H12">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I12">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J12">
+        <v>36</v>
+      </c>
+      <c r="K12">
         <v>38</v>
       </c>
-      <c r="K12">
-        <v>29</v>
-      </c>
       <c r="L12">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="M12">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="N12">
         <v>34</v>
       </c>
       <c r="O12">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P12">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="Q12">
-        <v>30.66666666666667</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="R12">
-        <v>32.2</v>
+        <v>33.8</v>
       </c>
       <c r="S12">
-        <v>30.32280814492209</v>
+        <v>35.41140407246105</v>
       </c>
       <c r="T12">
-        <v>31.61629476324428</v>
+        <v>34.96641873105175</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="2">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B13">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C13">
         <v>9</v>
@@ -1196,60 +1196,60 @@
         <v>2026</v>
       </c>
       <c r="E13">
+        <v>36</v>
+      </c>
+      <c r="F13">
         <v>37</v>
       </c>
-      <c r="F13">
-        <v>28</v>
-      </c>
       <c r="G13">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H13">
         <v>32</v>
       </c>
       <c r="I13">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J13">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K13">
+        <v>36</v>
+      </c>
+      <c r="L13">
         <v>38</v>
       </c>
-      <c r="L13">
-        <v>29</v>
-      </c>
       <c r="M13">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="N13">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="O13">
         <v>34</v>
       </c>
       <c r="P13">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q13">
-        <v>32.33333333333334</v>
+        <v>36</v>
       </c>
       <c r="R13">
-        <v>32.4</v>
+        <v>34.4</v>
       </c>
       <c r="S13">
-        <v>33.66140407246105</v>
+        <v>35.70570203623052</v>
       </c>
       <c r="T13">
-        <v>33.41086317549619</v>
+        <v>35.31094582070116</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B14">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>9</v>
@@ -1258,60 +1258,60 @@
         <v>2026</v>
       </c>
       <c r="E14">
+        <v>48</v>
+      </c>
+      <c r="F14">
+        <v>36</v>
+      </c>
+      <c r="G14">
+        <v>37</v>
+      </c>
+      <c r="H14">
         <v>35</v>
       </c>
-      <c r="F14">
-        <v>37</v>
-      </c>
-      <c r="G14">
-        <v>28</v>
-      </c>
-      <c r="H14">
-        <v>32</v>
-      </c>
       <c r="I14">
         <v>32</v>
       </c>
       <c r="J14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L14">
+        <v>36</v>
+      </c>
+      <c r="M14">
         <v>38</v>
       </c>
-      <c r="M14">
-        <v>29</v>
-      </c>
       <c r="N14">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="O14">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="P14">
         <v>34</v>
       </c>
       <c r="Q14">
-        <v>33.33333333333334</v>
+        <v>40.33333333333334</v>
       </c>
       <c r="R14">
-        <v>32.8</v>
+        <v>37.6</v>
       </c>
       <c r="S14">
-        <v>34.33070203623052</v>
+        <v>41.85285101811526</v>
       </c>
       <c r="T14">
-        <v>33.9405754503308</v>
+        <v>39.54063054713411</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>9</v>
@@ -1320,114 +1320,114 @@
         <v>2026</v>
       </c>
       <c r="E15">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F15">
+        <v>48</v>
+      </c>
+      <c r="G15">
+        <v>36</v>
+      </c>
+      <c r="H15">
+        <v>37</v>
+      </c>
+      <c r="I15">
         <v>35</v>
       </c>
-      <c r="G15">
-        <v>37</v>
-      </c>
-      <c r="H15">
-        <v>28</v>
-      </c>
-      <c r="I15">
-        <v>32</v>
-      </c>
       <c r="J15">
         <v>32</v>
       </c>
       <c r="K15">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L15">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M15">
+        <v>36</v>
+      </c>
+      <c r="N15">
         <v>38</v>
       </c>
-      <c r="N15">
-        <v>29</v>
-      </c>
       <c r="O15">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P15">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q15">
-        <v>39.33333333333334</v>
+        <v>37.33333333333334</v>
       </c>
       <c r="R15">
-        <v>35.6</v>
+        <v>36.8</v>
       </c>
       <c r="S15">
-        <v>40.16535101811526</v>
+        <v>34.92642550905763</v>
       </c>
       <c r="T15">
-        <v>37.96038363355387</v>
+        <v>35.69375369808941</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B16">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16">
         <v>2026</v>
       </c>
       <c r="E16">
+        <v>30</v>
+      </c>
+      <c r="F16">
         <v>28</v>
       </c>
-      <c r="F16">
-        <v>46</v>
-      </c>
       <c r="G16">
+        <v>48</v>
+      </c>
+      <c r="H16">
+        <v>36</v>
+      </c>
+      <c r="I16">
+        <v>37</v>
+      </c>
+      <c r="J16">
         <v>35</v>
       </c>
-      <c r="H16">
-        <v>37</v>
-      </c>
-      <c r="I16">
-        <v>28</v>
-      </c>
-      <c r="J16">
-        <v>32</v>
-      </c>
       <c r="K16">
         <v>32</v>
       </c>
       <c r="L16">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M16">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N16">
+        <v>36</v>
+      </c>
+      <c r="O16">
         <v>38</v>
       </c>
-      <c r="O16">
-        <v>29</v>
-      </c>
       <c r="P16">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="Q16">
-        <v>36.33333333333334</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="R16">
-        <v>34.8</v>
+        <v>35.8</v>
       </c>
       <c r="S16">
-        <v>34.08267550905763</v>
+        <v>32.46321275452881</v>
       </c>
       <c r="T16">
-        <v>34.64025575570258</v>
+        <v>33.79583579872627</v>
       </c>
     </row>
   </sheetData>
